--- a/vfm_report.xlsx
+++ b/vfm_report.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>Daraz</t>
         </is>
       </c>
     </row>
